--- a/course-design-2/outputs/tables/ch3/14_text_semantic_refinement_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/14_text_semantic_refinement_audit.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_修复前基线" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_修复后总体" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_完整vs去薪资语义" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_去薪资语义分位数" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_BGE截断统计" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_岗位大类技能覆盖" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_技能一级类型" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_公司身份调整影响" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_公司同时间简介冲突" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_公司版本重构前后" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_公司事件重构前后" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_回归检查" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="01_修复前基线" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_修复后总体" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_完整vs去薪资语义" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_去薪资语义分位数" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_BGE截断统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_岗位大类技能覆盖" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_技能一级类型" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_公司身份调整影响" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_公司同时间简介冲突" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_公司版本重构前后" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_公司事件重构前后" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_回归检查" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,11 +509,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>旧文本完全一致事件数</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>271</v>
+          <t>旧语义距离字段统计范围</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>岗位描述语义距离_完整</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -524,11 +526,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>旧语义距离P50</t>
+          <t>旧文本完全一致事件数</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7">
@@ -539,11 +541,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>旧语义距离P75</t>
+          <t>旧语义距离P50</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.010301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -554,11 +556,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>旧语义距离P90</t>
+          <t>旧语义距离P75</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.060088</v>
+        <v>0.010301</v>
       </c>
     </row>
     <row r="9">
@@ -569,11 +571,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>旧语义距离P95</t>
+          <t>旧语义距离P90</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.158988</v>
+        <v>0.060088</v>
       </c>
     </row>
     <row r="10">
@@ -584,11 +586,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>旧语义距离样本数</t>
+          <t>旧语义距离P95</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>423</v>
+        <v>0.158988</v>
       </c>
     </row>
     <row r="11">
@@ -599,11 +601,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>旧显著变化候选数_P90</t>
+          <t>旧语义距离样本数</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>43</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12">
@@ -614,11 +616,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>旧极端变化候选数_P95</t>
+          <t>旧显著变化候选数_P90</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -629,11 +631,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>薪资变化联动样本数</t>
+          <t>旧极端变化候选数_P95</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -644,11 +646,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>薪资稳定对照样本数</t>
+          <t>薪资变化联动样本数</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>393</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -659,11 +661,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>旧薪资变化组语义距离均值</t>
+          <t>薪资稳定对照样本数</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.013152</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16">
@@ -674,11 +676,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>旧薪资稳定组语义距离均值</t>
+          <t>旧薪资变化组语义距离均值</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.022308</v>
+        <v>0.013152</v>
       </c>
     </row>
     <row r="17">
@@ -689,13 +691,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>基线来源文件</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>data\processed\job_text_change_events.parquet；data\interim\job_text_version_corpus.parquet；data\processed\job_version_history.parquet</t>
-        </is>
+          <t>旧薪资稳定组语义距离均值</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.022308</v>
       </c>
     </row>
     <row r="18">
@@ -706,28 +706,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>基线捕获时间</t>
+          <t>基线来源文件</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-16 01:10:29</t>
+          <t>data\processed\job_text_change_events.parquet；data\interim\job_text_version_corpus.parquet；data\processed\job_version_history.parquet</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>公司层</t>
+          <t>岗位语义层</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>旧公司实体数</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4463</v>
+          <t>基线捕获时间</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:44:43</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -738,11 +740,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>旧正式公司实体数</t>
+          <t>旧公司实体数</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4452</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="21">
@@ -753,11 +755,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>旧公司简介版本数</t>
+          <t>旧正式公司实体数</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4887</v>
+        <v>4377</v>
       </c>
     </row>
     <row r="22">
@@ -768,11 +770,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>旧公司简介变化事件数</t>
+          <t>旧公司简介版本数</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>435</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="23">
@@ -783,11 +785,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>旧有变化公司数</t>
+          <t>旧公司简介变化事件数</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>44</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24">
@@ -798,11 +800,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>旧岗位观测快照行数</t>
+          <t>旧有变化公司数</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>172055</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -813,13 +815,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>旧映射方式分布</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>APPROVED_ALIAS=1；EXACT_NAME_LOCATION=74；EXACT_NORMALIZED_NAME=4377；HIGH_CONFIDENCE_MATCH=11</t>
-        </is>
+          <t>旧岗位观测快照行数</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>172055</v>
       </c>
     </row>
     <row r="26">
@@ -830,11 +830,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>旧旧口径_EXACT_NAME_LOCATION实体数</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>74</v>
+          <t>旧映射方式分布</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>APPROVED_ALIAS=1；EXACT_NORMALIZED_NAME=4376；HIGH_CONFIDENCE_MATCH=11；MULTI_LOCATION_AMBIGUOUS=33</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -845,13 +847,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>基线来源文件</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>data\processed\company_entity_map.parquet；data\processed\company_profile_history.parquet；data\processed\company_text_change_events.parquet</t>
-        </is>
+          <t>旧版统计范围_EXACT_NAME_LOCATION实体数</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -862,12 +862,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>基线来源文件</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>data\processed\company_entity_map.parquet；data\processed\company_profile_history.parquet；data\processed\company_text_change_events.parquet</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>公司层</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>基线捕获时间</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-09-16 01:10:29</t>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:46:18</t>
         </is>
       </c>
     </row>
@@ -939,20 +956,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4452</v>
+        <v>4377</v>
       </c>
       <c r="C2" t="n">
         <v>4377</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.016846</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -970,20 +987,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4463</v>
+        <v>4421</v>
       </c>
       <c r="C3" t="n">
         <v>4421</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-42</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.009410999999999999</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1001,20 +1018,20 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4887</v>
+        <v>3899</v>
       </c>
       <c r="C4" t="n">
         <v>3899</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>-988</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.202169</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -1093,20 +1110,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="C2" t="n">
         <v>235</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.45977</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -1124,20 +1141,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>16</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.636364</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1208,14 +1225,10 @@
       <c r="B2" t="n">
         <v>172063</v>
       </c>
-      <c r="C2" t="n">
-        <v>172063</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1224,7 +1237,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1237,14 +1250,10 @@
       <c r="B3" t="n">
         <v>30</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1253,7 +1262,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1266,14 +1275,10 @@
       <c r="B4" t="n">
         <v>17144</v>
       </c>
-      <c r="C4" t="n">
-        <v>17144</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1282,7 +1287,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1295,14 +1300,10 @@
       <c r="B5" t="n">
         <v>17148</v>
       </c>
-      <c r="C5" t="n">
-        <v>17148</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1311,7 +1312,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1324,14 +1325,10 @@
       <c r="B6" t="n">
         <v>17144</v>
       </c>
-      <c r="C6" t="n">
-        <v>17144</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1340,7 +1337,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1353,14 +1350,10 @@
       <c r="B7" t="n">
         <v>17144</v>
       </c>
-      <c r="C7" t="n">
-        <v>17144</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1362,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1382,14 +1375,10 @@
       <c r="B8" t="n">
         <v>17144</v>
       </c>
-      <c r="C8" t="n">
-        <v>17144</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1387,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1400,8 @@
       <c r="B9" t="n">
         <v>31</v>
       </c>
-      <c r="C9" t="n">
-        <v>46</v>
-      </c>
-      <c r="D9" t="n">
-        <v>15</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
         <v>0</v>
       </c>
@@ -1440,14 +1425,10 @@
       <c r="B10" t="n">
         <v>154919</v>
       </c>
-      <c r="C10" t="n">
-        <v>154919</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1456,7 +1437,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1469,14 +1450,10 @@
       <c r="B11" t="n">
         <v>10.0363</v>
       </c>
-      <c r="C11" t="n">
-        <v>10.0363</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1485,7 +1462,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1475,10 @@
       <c r="B12" t="n">
         <v>15311</v>
       </c>
-      <c r="C12" t="n">
-        <v>15311</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1514,7 +1487,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1527,14 +1500,10 @@
       <c r="B13" t="n">
         <v>1833</v>
       </c>
-      <c r="C13" t="n">
-        <v>1833</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1543,7 +1512,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1541,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>预期变化：字段多值审计改用版本签名的归一化口径（去首尾空格、空字符串统一归一为缺失）并采用 nunique(dropna=True)，「有值 vs 空值」不再计为字段冲突（仍会在版本签名中体现为不同状态）（禁止为匹配基线恢复原链接字段）</t>
+          <t>预期变化：字段多值审计改用版本签名的归一化统计范围（去首尾空格、空字符串统一归一为缺失）并采用 nunique(dropna=True)，「有值 vs 空值」不再计为字段冲突（仍会在版本签名中体现为不同状态）（禁止为匹配基线恢复原链接字段）</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1570,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>预期变化：同上：冲突留档口径迁移到变化事件表与 14 号版本审计表；另：Stage 01 已确定性修复源记录的公司属性语义槽位异常（公司性质/公司规模/公司所在地），相关字段的伪冲突随之减少（禁止为匹配基线恢复原链接字段）</t>
+          <t>预期变化：同上：冲突留档统计范围迁移到变化事件表与 14 号版本审计表；另：Stage 01 已确定性修复源记录的公司属性语义槽位异常（公司性质/公司规模/公司所在地），相关字段的伪冲突随之减少（禁止为匹配基线恢复原链接字段）</t>
         </is>
       </c>
     </row>
@@ -1643,14 +1612,10 @@
       <c r="B17" t="n">
         <v>9</v>
       </c>
-      <c r="C17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1659,7 +1624,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1672,14 +1637,10 @@
       <c r="B18" t="n">
         <v>21</v>
       </c>
-      <c r="C18" t="n">
-        <v>21</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1688,7 +1649,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1701,14 +1662,10 @@
       <c r="B19" t="n">
         <v>30</v>
       </c>
-      <c r="C19" t="n">
-        <v>30</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1717,7 +1674,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1787,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>去薪资口径显著变化候选数_P90</t>
+          <t>去薪资统计范围显著变化候选数_P90</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1840,7 +1797,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>去薪资口径极端变化候选数_P95</t>
+          <t>去薪资统计范围极端变化候选数_P95</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1850,7 +1807,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>旧完整口径显著候选数_P90</t>
+          <t>旧完整文本统计范围显著候选数_P90</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1860,7 +1817,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>旧完整口径极端候选数_P95</t>
+          <t>旧完整文本统计范围极端候选数_P95</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1880,7 +1837,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>因新口径进入显著候选的事件数</t>
+          <t>因新统计范围进入显著候选的事件数</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2004,42 +1961,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>完整口径均值</t>
+          <t>完整文本统计范围均值</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>完整口径中位数</t>
+          <t>完整文本统计范围中位数</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>完整口径P90</t>
+          <t>完整文本统计范围P90</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>完整口径P95</t>
+          <t>完整文本统计范围P95</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>去薪资口径均值</t>
+          <t>去薪资统计范围均值</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>去薪资口径中位数</t>
+          <t>去薪资统计范围中位数</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>去薪资口径P90</t>
+          <t>去薪资统计范围P90</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>去薪资口径P95</t>
+          <t>去薪资统计范围P95</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -2210,7 +2167,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2231,7 +2188,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2252,7 +2209,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2273,7 +2230,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2294,7 +2251,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>人工复核与业务口径</t>
+          <t>人工复核与业务统计范围</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2315,7 +2272,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>人工复核与业务口径</t>
+          <t>人工复核与业务统计范围</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2332,13 +2289,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>先统计真实分布分位数，再结合人工复核样本确认（去薪资口径为正式主判据）</t>
+          <t>先统计真实分布分位数，再结合人工复核样本确认（去薪资统计范围为正式主判据）</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>人工复核与业务口径</t>
+          <t>人工复核与业务统计范围</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2597,14 +2554,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>旧口径会按「名称@所在地」拆分出的行数</t>
+          <t>旧统计范围会按「名称@所在地」拆分出的行数</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>旧口径 EXACT_NAME_LOCATION 实体数</t>
+          <t>旧统计范围 EXACT_NAME_LOCATION 实体数</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/course-design-2/outputs/tables/ch3/14_text_semantic_refinement_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/14_text_semantic_refinement_audit.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_修复前基线" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_修复后总体" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_完整vs去薪资语义" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_去薪资语义分位数" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_BGE截断统计" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_岗位大类技能覆盖" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_技能一级类型" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_公司身份调整影响" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09_公司同时间简介冲突" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_公司版本重构前后" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_公司事件重构前后" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_回归检查" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_修复前基线" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_修复后总体" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_完整vs去薪资语义" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_去薪资语义分位数" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_BGE截断统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_岗位大类技能覆盖" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_技能一级类型" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_公司身份调整影响" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_公司同时间简介冲突" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_公司版本重构前后" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_公司事件重构前后" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_回归检查" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,13 +509,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>旧语义距离字段统计范围</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>岗位描述语义距离_完整</t>
-        </is>
+          <t>旧文本完全一致事件数</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>271</v>
       </c>
     </row>
     <row r="6">
@@ -526,11 +524,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>旧文本完全一致事件数</t>
+          <t>旧语义距离P50</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -541,11 +539,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>旧语义距离P50</t>
+          <t>旧语义距离P75</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.010301</v>
       </c>
     </row>
     <row r="8">
@@ -556,11 +554,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>旧语义距离P75</t>
+          <t>旧语义距离P90</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.010301</v>
+        <v>0.060088</v>
       </c>
     </row>
     <row r="9">
@@ -571,11 +569,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>旧语义距离P90</t>
+          <t>旧语义距离P95</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.060088</v>
+        <v>0.158988</v>
       </c>
     </row>
     <row r="10">
@@ -586,11 +584,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>旧语义距离P95</t>
+          <t>旧语义距离样本数</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.158988</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11">
@@ -601,11 +599,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>旧语义距离样本数</t>
+          <t>旧显著变化候选数_P90</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>423</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -616,11 +614,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>旧显著变化候选数_P90</t>
+          <t>旧极端变化候选数_P95</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -631,11 +629,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>旧极端变化候选数_P95</t>
+          <t>薪资变化联动样本数</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -646,11 +644,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>薪资变化联动样本数</t>
+          <t>薪资稳定对照样本数</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15">
@@ -661,11 +659,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>薪资稳定对照样本数</t>
+          <t>旧薪资变化组语义距离均值</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>393</v>
+        <v>0.013152</v>
       </c>
     </row>
     <row r="16">
@@ -676,11 +674,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>旧薪资变化组语义距离均值</t>
+          <t>旧薪资稳定组语义距离均值</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.013152</v>
+        <v>0.022308</v>
       </c>
     </row>
     <row r="17">
@@ -691,11 +689,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>旧薪资稳定组语义距离均值</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.022308</v>
+          <t>基线来源文件</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>data\processed\job_text_change_events.parquet；data\interim\job_text_version_corpus.parquet；data\processed\job_version_history.parquet</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -706,30 +706,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>基线来源文件</t>
+          <t>基线捕获时间</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>data\processed\job_text_change_events.parquet；data\interim\job_text_version_corpus.parquet；data\processed\job_version_history.parquet</t>
+          <t>2026-09-16 01:10:29</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>岗位语义层</t>
+          <t>公司层</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>基线捕获时间</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-10-09 13:44:43</t>
-        </is>
+          <t>旧公司实体数</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4463</v>
       </c>
     </row>
     <row r="20">
@@ -740,11 +738,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>旧公司实体数</t>
+          <t>旧正式公司实体数</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4421</v>
+        <v>4452</v>
       </c>
     </row>
     <row r="21">
@@ -755,11 +753,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>旧正式公司实体数</t>
+          <t>旧公司简介版本数</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4377</v>
+        <v>4887</v>
       </c>
     </row>
     <row r="22">
@@ -770,11 +768,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>旧公司简介版本数</t>
+          <t>旧公司简介变化事件数</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3899</v>
+        <v>435</v>
       </c>
     </row>
     <row r="23">
@@ -785,11 +783,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>旧公司简介变化事件数</t>
+          <t>旧有变化公司数</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>235</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
@@ -800,11 +798,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>旧有变化公司数</t>
+          <t>旧岗位观测快照行数</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>172055</v>
       </c>
     </row>
     <row r="25">
@@ -815,11 +813,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>旧岗位观测快照行数</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>172055</v>
+          <t>旧映射方式分布</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>APPROVED_ALIAS=1；EXACT_NAME_LOCATION=74；EXACT_NORMALIZED_NAME=4377；HIGH_CONFIDENCE_MATCH=11</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -830,13 +830,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>旧映射方式分布</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>APPROVED_ALIAS=1；EXACT_NORMALIZED_NAME=4376；HIGH_CONFIDENCE_MATCH=11；MULTI_LOCATION_AMBIGUOUS=33</t>
-        </is>
+          <t>旧旧口径_EXACT_NAME_LOCATION实体数</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="27">
@@ -847,11 +845,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>旧版统计范围_EXACT_NAME_LOCATION实体数</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
+          <t>基线来源文件</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>data\processed\company_entity_map.parquet；data\processed\company_profile_history.parquet；data\processed\company_text_change_events.parquet</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -862,29 +862,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>基线来源文件</t>
+          <t>基线捕获时间</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>data\processed\company_entity_map.parquet；data\processed\company_profile_history.parquet；data\processed\company_text_change_events.parquet</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>公司层</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>基线捕获时间</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-10-09 13:46:18</t>
+          <t>2026-09-16 01:10:29</t>
         </is>
       </c>
     </row>
@@ -956,20 +939,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4377</v>
+        <v>4452</v>
       </c>
       <c r="C2" t="n">
         <v>4377</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0.016846</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -987,20 +969,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4421</v>
+        <v>4463</v>
       </c>
       <c r="C3" t="n">
         <v>4421</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.009410999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1018,20 +999,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3899</v>
+        <v>4887</v>
       </c>
       <c r="C4" t="n">
         <v>3899</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-988</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0.202169</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -1110,20 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>235</v>
+        <v>435</v>
       </c>
       <c r="C2" t="n">
         <v>235</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0.45977</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -1141,20 +1120,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
         <v>16</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.636364</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1225,10 +1203,14 @@
       <c r="B2" t="n">
         <v>172063</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>172063</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1237,7 +1219,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1250,10 +1232,14 @@
       <c r="B3" t="n">
         <v>30</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1262,7 +1248,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1275,10 +1261,14 @@
       <c r="B4" t="n">
         <v>17144</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>17144</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1287,7 +1277,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1300,10 +1290,14 @@
       <c r="B5" t="n">
         <v>17148</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>17148</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1312,7 +1306,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1325,10 +1319,14 @@
       <c r="B6" t="n">
         <v>17144</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>17144</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1337,7 +1335,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1350,10 +1348,14 @@
       <c r="B7" t="n">
         <v>17144</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>17144</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1364,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1375,10 +1377,14 @@
       <c r="B8" t="n">
         <v>17144</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>17144</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1393,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1400,8 +1406,12 @@
       <c r="B9" t="n">
         <v>31</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>46</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
@@ -1425,10 +1435,14 @@
       <c r="B10" t="n">
         <v>154919</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>154919</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1437,7 +1451,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1450,10 +1464,14 @@
       <c r="B11" t="n">
         <v>10.0363</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>10.0363</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1462,7 +1480,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1475,10 +1493,14 @@
       <c r="B12" t="n">
         <v>15311</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>15311</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1487,7 +1509,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1500,10 +1522,14 @@
       <c r="B13" t="n">
         <v>1833</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>1833</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1512,7 +1538,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1567,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>预期变化：字段多值审计改用版本签名的归一化统计范围（去首尾空格、空字符串统一归一为缺失）并采用 nunique(dropna=True)，「有值 vs 空值」不再计为字段冲突（仍会在版本签名中体现为不同状态）（禁止为匹配基线恢复原链接字段）</t>
+          <t>预期变化：字段多值审计改用版本签名的归一化口径（去首尾空格、空字符串统一归一为缺失）并采用 nunique(dropna=True)，「有值 vs 空值」不再计为字段冲突（仍会在版本签名中体现为不同状态）（禁止为匹配基线恢复原链接字段）</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1596,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>预期变化：同上：冲突留档统计范围迁移到变化事件表与 14 号版本审计表；另：Stage 01 已确定性修复源记录的公司属性语义槽位异常（公司性质/公司规模/公司所在地），相关字段的伪冲突随之减少（禁止为匹配基线恢复原链接字段）</t>
+          <t>预期变化：同上：冲突留档口径迁移到变化事件表与 14 号版本审计表；另：Stage 01 已确定性修复源记录的公司属性语义槽位异常（公司性质/公司规模/公司所在地），相关字段的伪冲突随之减少（禁止为匹配基线恢复原链接字段）</t>
         </is>
       </c>
     </row>
@@ -1612,10 +1638,14 @@
       <c r="B17" t="n">
         <v>9</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1624,7 +1654,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1637,10 +1667,14 @@
       <c r="B18" t="n">
         <v>21</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>21</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1649,7 +1683,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1662,10 +1696,14 @@
       <c r="B19" t="n">
         <v>30</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1674,7 +1712,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>差异需人工确认（不得修改真实结果去匹配基线）</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1732,6 @@
           <t>发布时间</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="b">
         <v>1</v>
       </c>
@@ -1787,7 +1824,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>去薪资统计范围显著变化候选数_P90</t>
+          <t>去薪资口径显著变化候选数_P90</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1797,7 +1834,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>去薪资统计范围极端变化候选数_P95</t>
+          <t>去薪资口径极端变化候选数_P95</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1807,7 +1844,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>旧完整文本统计范围显著候选数_P90</t>
+          <t>旧完整口径显著候选数_P90</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1817,7 +1854,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>旧完整文本统计范围极端候选数_P95</t>
+          <t>旧完整口径极端候选数_P95</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1837,7 +1874,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>因新统计范围进入显著候选的事件数</t>
+          <t>因新口径进入显著候选的事件数</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2039,19 +2076,6 @@
       <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Embedding 距离不是可加性分解，该差值仅作诊断，禁止解释为「薪资文本贡献率」</t>
@@ -2067,19 +2091,6 @@
       <c r="B3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Embedding 距离不是可加性分解，该差值仅作诊断，禁止解释为「薪资文本贡献率」</t>
@@ -2095,19 +2106,6 @@
       <c r="B4" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Embedding 距离不是可加性分解，该差值仅作诊断，禁止解释为「薪资文本贡献率」</t>
@@ -2161,13 +2159,12 @@
           <t>岗位描述语义距离_去薪资P50</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2182,13 +2179,12 @@
           <t>岗位描述语义距离_去薪资P75</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2203,13 +2199,12 @@
           <t>岗位描述语义距离_去薪资P90</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2224,13 +2219,12 @@
           <t>岗位描述语义距离_去薪资P95</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2248,10 +2242,9 @@
       <c r="B6" t="n">
         <v>0.9</v>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>人工复核与业务统计范围</t>
+          <t>人工复核与业务口径</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2269,10 +2262,9 @@
       <c r="B7" t="n">
         <v>0.95</v>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>人工复核与业务统计范围</t>
+          <t>人工复核与业务口径</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2289,13 +2281,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>先统计真实分布分位数，再结合人工复核样本确认（去薪资统计范围为正式主判据）</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>先统计真实分布分位数，再结合人工复核样本确认（去薪资口径为正式主判据）</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>人工复核与业务统计范围</t>
+          <t>人工复核与业务口径</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2554,14 +2545,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>旧统计范围会按「名称@所在地」拆分出的行数</t>
+          <t>旧口径会按「名称@所在地」拆分出的行数</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>旧统计范围 EXACT_NAME_LOCATION 实体数</t>
+          <t>旧口径 EXACT_NAME_LOCATION 实体数</t>
         </is>
       </c>
       <c r="B6" t="n">
